--- a/exports/trend_1d/POLYCAB_full_report.xlsx
+++ b/exports/trend_1d/POLYCAB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:U47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.93</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43600</v>
+        <v>43601</v>
       </c>
       <c r="H2" t="n">
-        <v>620.65</v>
+        <v>599.35</v>
       </c>
       <c r="I2" t="n">
         <v>604.14130935</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.43</v>
+        <v>-6.74</v>
       </c>
       <c r="L2" t="n">
-        <v>6.33</v>
+        <v>9.24</v>
       </c>
       <c r="M2" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" t="n">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="O2" t="n">
         <v>0.13</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.35</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43643</v>
+        <v>43644</v>
       </c>
       <c r="H3" t="n">
-        <v>613.45</v>
+        <v>622.05</v>
       </c>
       <c r="I3" t="n">
         <v>621.6786307619036</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.35</v>
+        <v>-3.79</v>
       </c>
       <c r="L3" t="n">
         <v>5.61</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.07</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H4" t="n">
-        <v>620.15</v>
+        <v>600.9</v>
       </c>
       <c r="I4" t="n">
         <v>606.6062711986702</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.31</v>
+        <v>-3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>3.83</v>
       </c>
       <c r="M4" t="n">
         <v>0.57</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43705</v>
+        <v>43706</v>
       </c>
       <c r="H5" t="n">
-        <v>571.1</v>
+        <v>593.65</v>
       </c>
       <c r="I5" t="n">
         <v>586.8101143866397</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K5" t="n">
-        <v>4.96</v>
+        <v>1.21</v>
       </c>
       <c r="L5" t="n">
         <v>7.66</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.84</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43851</v>
+        <v>43852</v>
       </c>
       <c r="H6" t="n">
-        <v>1082.75</v>
+        <v>994.3</v>
       </c>
       <c r="I6" t="n">
         <v>1013.072599072606</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K6" t="n">
-        <v>82.39</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>2.75</v>
@@ -783,7 +854,7 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.11</v>
+        <v>8.17</v>
       </c>
       <c r="O6" t="n">
         <v>3.95</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>22.12</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43880</v>
+        <v>43881</v>
       </c>
       <c r="H7" t="n">
-        <v>1077.75</v>
+        <v>1138.1</v>
       </c>
       <c r="I7" t="n">
         <v>1093.523346590417</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.390000000000001</v>
+        <v>-14.46</v>
       </c>
       <c r="L7" t="n">
-        <v>13.65</v>
+        <v>16.43</v>
       </c>
       <c r="M7" t="n">
         <v>4.32</v>
       </c>
       <c r="N7" t="n">
-        <v>4.61</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>-8.17</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>12.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H8" t="n">
-        <v>1005.05</v>
+        <v>875.25</v>
       </c>
       <c r="I8" t="n">
         <v>996.6683047990065</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-11.69</v>
+        <v>-23.1</v>
       </c>
       <c r="L8" t="n">
-        <v>13.72</v>
+        <v>25.31</v>
       </c>
       <c r="M8" t="n">
         <v>5.42</v>
       </c>
       <c r="N8" t="n">
-        <v>8.66</v>
+        <v>12.91</v>
       </c>
       <c r="O8" t="n">
         <v>5.6</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>27.95</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H9" t="n">
-        <v>713.35</v>
+        <v>749</v>
       </c>
       <c r="I9" t="n">
         <v>722.8001370867396</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K9" t="n">
-        <v>18.5</v>
+        <v>14.42</v>
       </c>
       <c r="L9" t="n">
         <v>18</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.82</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H10" t="n">
-        <v>842.2</v>
+        <v>830.15</v>
       </c>
       <c r="I10" t="n">
         <v>838.9861710522603</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K10" t="n">
-        <v>12.44</v>
+        <v>10.83</v>
       </c>
       <c r="L10" t="n">
         <v>5.86</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.1</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44126</v>
+        <v>44127</v>
       </c>
       <c r="H11" t="n">
-        <v>832.05</v>
+        <v>881.25</v>
       </c>
       <c r="I11" t="n">
         <v>862.2788974603812</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.23</v>
+        <v>-6.16</v>
       </c>
       <c r="L11" t="n">
         <v>9.619999999999999</v>
@@ -1068,7 +1199,7 @@
         <v>2.24</v>
       </c>
       <c r="N11" t="n">
-        <v>4.86</v>
+        <v>5.91</v>
       </c>
       <c r="O11" t="n">
         <v>-1.43</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.27</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44403</v>
+        <v>44404</v>
       </c>
       <c r="H12" t="n">
-        <v>1858.5</v>
+        <v>1802.5</v>
       </c>
       <c r="I12" t="n">
         <v>1852.190059287703</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K12" t="n">
-        <v>110.89</v>
+        <v>104.54</v>
       </c>
       <c r="L12" t="n">
         <v>5.24</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10</v>
+      </c>
+      <c r="U12" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>11.95</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44435</v>
+        <v>44438</v>
       </c>
       <c r="H13" t="n">
-        <v>1894.55</v>
+        <v>2033.55</v>
       </c>
       <c r="I13" t="n">
         <v>1972.982691175057</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.11</v>
+        <v>-12.82</v>
       </c>
       <c r="L13" t="n">
-        <v>8.52</v>
+        <v>13.62</v>
       </c>
       <c r="M13" t="n">
         <v>1.47</v>
       </c>
       <c r="N13" t="n">
-        <v>5.01</v>
+        <v>7.34</v>
       </c>
       <c r="O13" t="n">
         <v>-3.01</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.67</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H14" t="n">
-        <v>2294.15</v>
+        <v>2221.1</v>
       </c>
       <c r="I14" t="n">
         <v>2271.802018182216</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K14" t="n">
-        <v>12.82</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>6.45</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>16.1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44540</v>
+        <v>44543</v>
       </c>
       <c r="H15" t="n">
-        <v>2471.65</v>
+        <v>2545.3</v>
       </c>
       <c r="I15" t="n">
         <v>2500.356747351777</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K15" t="n">
-        <v>-11.28</v>
+        <v>-14.6</v>
       </c>
       <c r="L15" t="n">
-        <v>14.53</v>
+        <v>17.48</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.75</v>
       </c>
       <c r="N15" t="n">
         <v>4.13</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>10.01</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H16" t="n">
-        <v>2325.85</v>
+        <v>2281.85</v>
       </c>
       <c r="I16" t="n">
         <v>2290.540392999607</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.619999999999999</v>
+        <v>-10.35</v>
       </c>
       <c r="L16" t="n">
-        <v>9.029999999999999</v>
+        <v>13.28</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4</v>
+        <v>1.97</v>
       </c>
       <c r="N16" t="n">
         <v>4.04</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>11.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44573</v>
+        <v>44574</v>
       </c>
       <c r="H17" t="n">
-        <v>2480.8</v>
+        <v>2685.15</v>
       </c>
       <c r="I17" t="n">
         <v>2544.533645087662</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.720000000000001</v>
+        <v>-17.67</v>
       </c>
       <c r="L17" t="n">
-        <v>11.09</v>
+        <v>18.23</v>
       </c>
       <c r="M17" t="n">
         <v>1.89</v>
       </c>
       <c r="N17" t="n">
-        <v>2.31</v>
+        <v>8.24</v>
       </c>
       <c r="O17" t="n">
         <v>-1.89</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>12.23</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H18" t="n">
-        <v>2510.85</v>
+        <v>2463.4</v>
       </c>
       <c r="I18" t="n">
         <v>2482.902539096947</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.49</v>
+        <v>-8.26</v>
       </c>
       <c r="L18" t="n">
-        <v>7.53</v>
+        <v>11.46</v>
       </c>
       <c r="M18" t="n">
         <v>0.64</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>11.34</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H19" t="n">
-        <v>2469.2</v>
+        <v>2654.45</v>
       </c>
       <c r="I19" t="n">
         <v>2471.667151571544</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.24</v>
+        <v>-7.76</v>
       </c>
       <c r="L19" t="n">
-        <v>4.93</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>2.67</v>
       </c>
       <c r="N19" t="n">
-        <v>4.57</v>
+        <v>7.5</v>
       </c>
       <c r="O19" t="n">
         <v>-1.89</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>11.99</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H20" t="n">
-        <v>2467.25</v>
+        <v>2428.3</v>
       </c>
       <c r="I20" t="n">
         <v>2440.653413445475</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K20" t="n">
-        <v>-7.05</v>
+        <v>-8.52</v>
       </c>
       <c r="L20" t="n">
-        <v>7.89</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>0.92</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>14.01</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44771</v>
+        <v>44774</v>
       </c>
       <c r="H21" t="n">
-        <v>2317.45</v>
+        <v>2342.3</v>
       </c>
       <c r="I21" t="n">
         <v>2332.438648393576</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K21" t="n">
-        <v>4.56</v>
+        <v>3.54</v>
       </c>
       <c r="L21" t="n">
         <v>8.300000000000001</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H22" t="n">
-        <v>2580.8</v>
+        <v>2495.05</v>
       </c>
       <c r="I22" t="n">
         <v>2497.767584189892</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K22" t="n">
-        <v>10.18</v>
+        <v>6.52</v>
       </c>
       <c r="L22" t="n">
         <v>2.3</v>
@@ -1695,7 +1958,7 @@
         <v>2.38</v>
       </c>
       <c r="N22" t="n">
-        <v>3.09</v>
+        <v>3.32</v>
       </c>
       <c r="O22" t="n">
         <v>1.07</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44851</v>
+        <v>44852</v>
       </c>
       <c r="H23" t="n">
-        <v>2618.8</v>
+        <v>2749.05</v>
       </c>
       <c r="I23" t="n">
         <v>2702.260817451587</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.96</v>
+        <v>-10.18</v>
       </c>
       <c r="L23" t="n">
-        <v>8.210000000000001</v>
+        <v>11.02</v>
       </c>
       <c r="M23" t="n">
         <v>1.23</v>
       </c>
       <c r="N23" t="n">
-        <v>3.58</v>
+        <v>4.97</v>
       </c>
       <c r="O23" t="n">
         <v>-3.32</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>10.42</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44881</v>
+        <v>44882</v>
       </c>
       <c r="H24" t="n">
-        <v>2619.65</v>
+        <v>2570.1</v>
       </c>
       <c r="I24" t="n">
         <v>2595.04707869397</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.71</v>
+        <v>-6.51</v>
       </c>
       <c r="L24" t="n">
-        <v>6.43</v>
+        <v>6.83</v>
       </c>
       <c r="M24" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="N24" t="n">
         <v>2.61</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.59</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44902</v>
+        <v>44903</v>
       </c>
       <c r="H25" t="n">
-        <v>2706.65</v>
+        <v>2732.45</v>
       </c>
       <c r="I25" t="n">
         <v>2709.656981759911</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.31</v>
+        <v>-6.32</v>
       </c>
       <c r="L25" t="n">
         <v>6.61</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>6.87</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H26" t="n">
-        <v>2981.45</v>
+        <v>2753.9</v>
       </c>
       <c r="I26" t="n">
         <v>2777.678629995844</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.109999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="L26" t="n">
         <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0.62</v>
+        <v>7.63</v>
       </c>
       <c r="O26" t="n">
         <v>0.95</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>13.32</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44944</v>
+        <v>44945</v>
       </c>
       <c r="H27" t="n">
-        <v>2753.6</v>
+        <v>2828.6</v>
       </c>
       <c r="I27" t="n">
         <v>2787.955492526993</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01</v>
+        <v>-2.71</v>
       </c>
       <c r="L27" t="n">
         <v>7.67</v>
@@ -1980,7 +2303,7 @@
         <v>0.98</v>
       </c>
       <c r="N27" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
         <v>-7.63</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.4</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45002</v>
+        <v>45005</v>
       </c>
       <c r="H28" t="n">
-        <v>2884.4</v>
+        <v>2864.45</v>
       </c>
       <c r="I28" t="n">
         <v>2875.929766262292</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K28" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="L28" t="n">
         <v>3.74</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.34</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45026</v>
+        <v>45027</v>
       </c>
       <c r="H29" t="n">
-        <v>2975</v>
+        <v>3045.5</v>
       </c>
       <c r="I29" t="n">
         <v>2981.696408743348</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.86</v>
+        <v>-6.32</v>
       </c>
       <c r="L29" t="n">
-        <v>4.17</v>
+        <v>6.65</v>
       </c>
       <c r="M29" t="n">
         <v>0.9</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.67</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H30" t="n">
-        <v>5154.15</v>
+        <v>5023.15</v>
       </c>
       <c r="I30" t="n">
         <v>5061.675953650884</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K30" t="n">
-        <v>69.23999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="L30" t="n">
         <v>1.99</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.26</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="H31" t="n">
-        <v>5234.55</v>
+        <v>5341.6</v>
       </c>
       <c r="I31" t="n">
         <v>5335.977902487107</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.21</v>
+        <v>-6.34</v>
       </c>
       <c r="L31" t="n">
         <v>8.16</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.24</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45299</v>
+        <v>45300</v>
       </c>
       <c r="H32" t="n">
-        <v>5344.25</v>
+        <v>4867.1</v>
       </c>
       <c r="I32" t="n">
         <v>5315.252321098108</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K32" t="n">
-        <v>0.05</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>0.16</v>
       </c>
       <c r="N32" t="n">
-        <v>4.63</v>
+        <v>8.93</v>
       </c>
       <c r="O32" t="n">
         <v>2.05</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>15.74</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45338</v>
+        <v>45341</v>
       </c>
       <c r="H33" t="n">
-        <v>4670</v>
+        <v>4768.6</v>
       </c>
       <c r="I33" t="n">
         <v>4739.112829522412</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K33" t="n">
-        <v>4.05</v>
+        <v>2.02</v>
       </c>
       <c r="L33" t="n">
         <v>11.01</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.79</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="H34" t="n">
-        <v>6634.1</v>
+        <v>6546.6</v>
       </c>
       <c r="I34" t="n">
         <v>6624.429913514529</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K34" t="n">
-        <v>39.12</v>
+        <v>37.29</v>
       </c>
       <c r="L34" t="n">
         <v>2.8</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45503</v>
+        <v>45504</v>
       </c>
       <c r="H35" t="n">
-        <v>6681.75</v>
+        <v>6858.2</v>
       </c>
       <c r="I35" t="n">
         <v>6766.980758587708</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.06</v>
+        <v>-4.76</v>
       </c>
       <c r="L35" t="n">
-        <v>2.62</v>
+        <v>5.12</v>
       </c>
       <c r="M35" t="n">
         <v>0.5600000000000001</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45583</v>
+        <v>45586</v>
       </c>
       <c r="H36" t="n">
-        <v>7120.4</v>
+        <v>6849.75</v>
       </c>
       <c r="I36" t="n">
         <v>6904.220726976382</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K36" t="n">
-        <v>3.82</v>
+        <v>-0.12</v>
       </c>
       <c r="L36" t="n">
         <v>8.01</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.54</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H37" t="n">
-        <v>6872.65</v>
+        <v>7044</v>
       </c>
       <c r="I37" t="n">
         <v>6943.472719964584</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.33</v>
+        <v>-2.84</v>
       </c>
       <c r="L37" t="n">
         <v>5.75</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.75</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H38" t="n">
-        <v>7118.35</v>
+        <v>7091.85</v>
       </c>
       <c r="I38" t="n">
         <v>7118.086384971942</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K38" t="n">
-        <v>1.06</v>
+        <v>0.68</v>
       </c>
       <c r="L38" t="n">
         <v>3.06</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.16</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H39" t="n">
-        <v>5412.5</v>
+        <v>5506</v>
       </c>
       <c r="I39" t="n">
         <v>5456.827256845561</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K39" t="n">
-        <v>23.68</v>
+        <v>22.36</v>
       </c>
       <c r="L39" t="n">
         <v>4.91</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H40" t="n">
-        <v>7347</v>
+        <v>7227</v>
       </c>
       <c r="I40" t="n">
         <v>7299.649183500997</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K40" t="n">
-        <v>33.44</v>
+        <v>31.26</v>
       </c>
       <c r="L40" t="n">
         <v>2.18</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>9</v>
+      </c>
+      <c r="U40" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.76</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="H41" t="n">
-        <v>7439</v>
+        <v>7603</v>
       </c>
       <c r="I41" t="n">
         <v>7585.078673849507</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.93</v>
+        <v>-5.2</v>
       </c>
       <c r="L41" t="n">
-        <v>3.15</v>
+        <v>5.83</v>
       </c>
       <c r="M41" t="n">
         <v>0.35</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="H42" t="n">
-        <v>7555</v>
+        <v>7323.5</v>
       </c>
       <c r="I42" t="n">
         <v>7343.888218139105</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.63</v>
+        <v>-3.68</v>
       </c>
       <c r="L42" t="n">
-        <v>2.64</v>
+        <v>3.94</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>1.86</v>
+        <v>3.06</v>
       </c>
       <c r="O42" t="n">
         <v>2.2</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H43" t="n">
-        <v>7036.5</v>
+        <v>7505</v>
       </c>
       <c r="I43" t="n">
         <v>7411.408212032726</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>3.92</v>
+        <v>-2.48</v>
       </c>
       <c r="L43" t="n">
-        <v>2.93</v>
+        <v>5.13</v>
       </c>
       <c r="M43" t="n">
-        <v>1.24</v>
+        <v>5.17</v>
       </c>
       <c r="N43" t="n">
-        <v>4.16</v>
+        <v>6.66</v>
       </c>
       <c r="O43" t="n">
         <v>-3.06</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.34</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="H44" t="n">
-        <v>8228.5</v>
+        <v>7723</v>
       </c>
       <c r="I44" t="n">
         <v>7990.780263129471</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K44" t="n">
-        <v>9.640000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="L44" t="n">
         <v>1.93</v>
@@ -2949,7 +3476,7 @@
         <v>2.44</v>
       </c>
       <c r="N44" t="n">
-        <v>3.78</v>
+        <v>6.14</v>
       </c>
       <c r="O44" t="n">
         <v>6.66</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>14.75</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H45" t="n">
-        <v>7607</v>
+        <v>7728</v>
       </c>
       <c r="I45" t="n">
         <v>7619.800907752956</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K45" t="n">
-        <v>1.5</v>
+        <v>-0.06</v>
       </c>
       <c r="L45" t="n">
         <v>8.289999999999999</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.51</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H46" t="n">
-        <v>9584</v>
+        <v>9401</v>
       </c>
       <c r="I46" t="n">
         <v>9415.982128140688</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K46" t="n">
-        <v>24.02</v>
+        <v>21.65</v>
       </c>
       <c r="L46" t="n">
         <v>3.78</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3123,6 +3686,14 @@
       <c r="Q47" t="n">
         <v>79</v>
       </c>
+      <c r="R47" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6347,7 +6918,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.6</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="6">
@@ -6357,7 +6928,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -6367,7 +6938,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8">
@@ -6377,7 +6948,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -6387,7 +6958,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -6397,7 +6968,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129.4</v>
+        <v>131.6</v>
       </c>
     </row>
     <row r="11">
@@ -6407,7 +6978,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -6417,7 +6988,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -6427,7 +6998,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -6437,7 +7008,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.41</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="15">
@@ -6447,7 +7018,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.4</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="16">
@@ -6457,7 +7028,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="17">
@@ -6467,7 +7038,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>110.89</v>
+        <v>104.54</v>
       </c>
     </row>
     <row r="18">
@@ -6477,7 +7048,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6487,7 +7058,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.29</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="20">
@@ -6497,7 +7068,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.86</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="21">
@@ -6507,7 +7078,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>25.31</v>
       </c>
     </row>
     <row r="22">
@@ -6517,7 +7088,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -6527,7 +7098,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -6537,7 +7108,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="25">
@@ -6557,7 +7128,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.27</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="27">
@@ -6567,7 +7138,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="28">
@@ -6577,7 +7148,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
